--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>641.36</v>
+        <v>635.92</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1329.43</v>
+        <v>1363.04</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4639.36</v>
+        <v>4663.32</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1363.28</v>
+        <v>1361.87</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1291.55</v>
+        <v>1287.99</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11496.22</v>
+        <v>11593.79</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1311.42</v>
+        <v>1305.79</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1188.87</v>
+        <v>1178.73</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41082.5</v>
+        <v>40989.25</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4419.04</v>
+        <v>4482.27</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>322.47</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>772.78</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1575.08</v>
+        <v>1582.23</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4612.71</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1312.57</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6264.61</v>
+        <v>6277.96</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35268.44</v>
+        <v>35515.26</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39187.16</v>
+        <v>39063.38</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30038.56</v>
+        <v>29553.81</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6003.84</v>
+        <v>5907.57</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,68 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4932.08</v>
+        <v>4904.73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2380-1438-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>25246.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5349-2606-CM25</t>
+          <t>1554-166-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>635.92</v>
+        <v>1704.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5349-191-CM26</t>
+          <t>5349-2225-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1363.04</v>
+        <v>1481.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1554-171-CM26</t>
+          <t>5349-2606-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4663.32</v>
+        <v>635.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5349-369-CM26</t>
+          <t>5349-191-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1361.87</v>
+        <v>1363.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5349-540-CM26</t>
+          <t>1554-171-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1287.99</v>
+        <v>4663.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079486-48-CM26</t>
+          <t>5349-369-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11593.79</v>
+        <v>1361.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1554-748-CM26</t>
+          <t>5349-540-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1305.79</v>
+        <v>1287.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5349-899-CM26</t>
+          <t>1079486-48-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SECCIÓN COMPRAS III ZONA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1178.73</v>
+        <v>11593.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2380-921-CM26</t>
+          <t>1554-748-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>40989.25</v>
+        <v>1305.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1554-941-CM26</t>
+          <t>5349-899-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4482.27</v>
+        <v>1178.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2322-384-CM26</t>
+          <t>2380-921-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>326.25</v>
+        <v>40989.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2322-380-CM26</t>
+          <t>1554-941-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>772.78</v>
+        <v>4482.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5349-1183-CM26</t>
+          <t>2322-380-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1582.23</v>
+        <v>772.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>2322-384-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4700.4</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>5349-1183-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1309.09</v>
+        <v>1582.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2322-540-CM26</t>
+          <t>2322-382-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6277.96</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2380-1311-CM26</t>
+          <t>5349-1254-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35515.26</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2380-1314-CM26</t>
+          <t>2322-540-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39063.38</v>
+        <v>6277.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2380-1334-CM26</t>
+          <t>2380-1311-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>29553.81</v>
+        <v>35515.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1077275-25-CM26</t>
+          <t>2380-1314-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5907.57</v>
+        <v>39063.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2380-1372-CM26</t>
+          <t>2380-1334-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4904.73</v>
+        <v>29553.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2380-1438-CM26</t>
+          <t>1077275-25-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,6 +1850,128 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>5907.57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2380-1372-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>4904.73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2380-1438-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>25246.75</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1554-166-CM25</t>
+          <t>5349-58-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.238.721-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1704.41</v>
+        <v>1370.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5349-2225-CM25</t>
+          <t>5349-59-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1481.65</v>
+        <v>1370.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5349-2606-CM25</t>
+          <t>5349-60-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>635.92</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5349-191-CM26</t>
+          <t>1554-165-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1363.04</v>
+        <v>1692.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1554-171-CM26</t>
+          <t>1554-164-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4663.32</v>
+        <v>6326.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5349-369-CM26</t>
+          <t>1554-166-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1361.87</v>
+        <v>1704.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5349-540-CM26</t>
+          <t>5349-397-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1287.99</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1079486-48-CM26</t>
+          <t>5349-573-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11593.79</v>
+        <v>1254.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1554-748-CM26</t>
+          <t>5349-574-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1305.79</v>
+        <v>1254.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5349-899-CM26</t>
+          <t>5349-575-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1178.73</v>
+        <v>1003.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2380-921-CM26</t>
+          <t>778993-67-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40989.25</v>
+        <v>1610.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1554-941-CM26</t>
+          <t>5349-845-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4482.27</v>
+        <v>1249.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-380-CM26</t>
+          <t>2380-1153-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>772.78</v>
+        <v>68073.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2322-384-CM26</t>
+          <t>1554-1162-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>326.25</v>
+        <v>927.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5349-1183-CM26</t>
+          <t>5349-1558-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1582.23</v>
+        <v>965.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>5349-1697-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4700.4</v>
+        <v>3548.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>5349-1696-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1309.09</v>
+        <v>2129.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2322-540-CM26</t>
+          <t>5349-1763-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6277.96</v>
+        <v>2748.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2380-1311-CM26</t>
+          <t>5349-1764-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>35515.26</v>
+        <v>7726.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2380-1314-CM26</t>
+          <t>5349-1940-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>39063.38</v>
+        <v>613.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2380-1334-CM26</t>
+          <t>5349-2225-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29553.81</v>
+        <v>1481.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1077275-25-CM26</t>
+          <t>5349-2292-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5907.57</v>
+        <v>1245.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2380-1372-CM26</t>
+          <t>2322-926-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4904.73</v>
+        <v>4881.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2380-1438-CM26</t>
+          <t>5349-2606-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,6 +1972,1409 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
+        <v>635.92</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5349-191-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1363.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1554-171-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>4663.32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5349-369-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1361.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5349-540-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1287.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1079486-48-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.505.105-7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS III ZONA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>11593.79</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1554-748-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1305.79</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5349-899-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1178.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2380-921-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>40989.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1554-941-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>4482.27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2322-384-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>326.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2322-380-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>772.78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5349-1183-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1582.23</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2322-382-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>4700.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5349-1254-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1309.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2322-540-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>6277.96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2380-1311-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ECOLES SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.087.242-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>35515.26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2380-1314-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ECOLES SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.087.242-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>39063.38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2380-1334-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ECOLES SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.087.242-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>29553.81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1077275-25-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>5907.57</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2380-1372-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>4904.73</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2380-1415-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMERCIAL EL TORO SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>5127.18</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2380-1435-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>4914.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2380-1438-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>25246.75</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1554-166-CM25</t>
+          <t>5349-397-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.238.721-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1704.41</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5349-397-CM25</t>
+          <t>5349-575-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>845.28</v>
+        <v>1003.83</v>
       </c>
     </row>
     <row r="9">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5349-575-CM25</t>
+          <t>778993-67-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1003.83</v>
+        <v>1610.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>778993-67-CM25</t>
+          <t>5349-845-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.544.929-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1610.67</v>
+        <v>1249.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5349-845-CM25</t>
+          <t>2380-1153-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1249.71</v>
+        <v>68073.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2380-1153-CM25</t>
+          <t>1554-1162-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>68073.13</v>
+        <v>927.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1554-1162-CM25</t>
+          <t>5349-1558-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>927.74</v>
+        <v>965.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5349-1558-CM25</t>
+          <t>5349-1696-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>965.87</v>
+        <v>2129.08</v>
       </c>
     </row>
     <row r="17">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5349-1696-CM25</t>
+          <t>5349-1763-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2129.08</v>
+        <v>2748.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5349-1763-CM25</t>
+          <t>5349-1764-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2748.61</v>
+        <v>7726.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5349-1764-CM25</t>
+          <t>5349-1940-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7726.64</v>
+        <v>613.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5349-1940-CM25</t>
+          <t>5349-2225-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>613.11</v>
+        <v>1481.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5349-2225-CM25</t>
+          <t>5349-2292-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1481.65</v>
+        <v>1245.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5349-2292-CM25</t>
+          <t>2322-926-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1245.59</v>
+        <v>4881.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2322-926-CM25</t>
+          <t>5349-2606-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4881.44</v>
+        <v>635.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5349-2606-CM25</t>
+          <t>5349-191-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>635.92</v>
+        <v>1363.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5349-191-CM26</t>
+          <t>1554-171-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1363.04</v>
+        <v>4663.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1554-171-CM26</t>
+          <t>5349-369-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4663.32</v>
+        <v>1361.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5349-369-CM26</t>
+          <t>5349-540-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1361.87</v>
+        <v>1287.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5349-540-CM26</t>
+          <t>1079486-48-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1287.99</v>
+        <v>11593.79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079486-48-CM26</t>
+          <t>1554-748-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>11593.79</v>
+        <v>1305.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1554-748-CM26</t>
+          <t>5349-899-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1305.79</v>
+        <v>1178.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5349-899-CM26</t>
+          <t>2380-921-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1178.73</v>
+        <v>40989.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2380-921-CM26</t>
+          <t>1554-941-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>40989.25</v>
+        <v>4482.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1554-941-CM26</t>
+          <t>2322-380-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4482.27</v>
+        <v>772.78</v>
       </c>
     </row>
     <row r="35">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2322-380-CM26</t>
+          <t>5349-1183-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>772.78</v>
+        <v>1582.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5349-1183-CM26</t>
+          <t>2322-382-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1582.23</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>5349-1254-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4700.4</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>2322-540-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1309.09</v>
+        <v>6277.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2322-540-CM26</t>
+          <t>2380-1311-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6277.96</v>
+        <v>35515.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2380-1311-CM26</t>
+          <t>2380-1314-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35515.26</v>
+        <v>39063.38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2380-1314-CM26</t>
+          <t>2380-1334-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>39063.38</v>
+        <v>29553.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2380-1334-CM26</t>
+          <t>1077275-25-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>29553.81</v>
+        <v>5907.57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1077275-25-CM26</t>
+          <t>2380-1372-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5907.57</v>
+        <v>4904.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2380-1372-CM26</t>
+          <t>2380-1415-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4904.73</v>
+        <v>5127.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2380-1415-CM26</t>
+          <t>2380-1435-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5127.18</v>
+        <v>4914.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2380-1435-CM26</t>
+          <t>2380-1438-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4914.75</v>
+        <v>25246.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2380-1438-CM26</t>
+          <t>5349-1864-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,7 +3375,129 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>25246.75</v>
+        <v>1362.18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5349-1927-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>3566.07</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5349-1928-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3566.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -1111,7 +1111,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1298,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1851,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2221,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2286,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2412,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2538,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2603,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2729,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3160,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1498,7 +1498,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5349-1763-CM25</t>
+          <t>5349-1764-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2748.61</v>
+        <v>7726.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5349-1764-CM25</t>
+          <t>5349-1763-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7726.64</v>
+        <v>2748.61</v>
       </c>
     </row>
     <row r="20">
@@ -2490,7 +2490,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2322-380-CM26</t>
+          <t>2322-384-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>772.78</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2322-384-CM26</t>
+          <t>2322-380-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>326.25</v>
+        <v>772.78</v>
       </c>
     </row>
     <row r="36">
@@ -3421,7 +3421,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5349-1927-CM26</t>
+          <t>5349-1928-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5349-1928-CM26</t>
+          <t>5349-1927-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3538,6 +3538,193 @@
       </c>
       <c r="M50" s="2" t="n">
         <v>3566.07</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5349-1977-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>1111.39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5349-1978-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>1234.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>778993-147-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.946.100-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>5143.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5349-397-CM25</t>
+          <t>1554-166-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>845.28</v>
+        <v>1704.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5349-575-CM25</t>
+          <t>5349-397-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1003.83</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="9">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>778993-67-CM25</t>
+          <t>5349-575-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,32 +1103,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.544.929-2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1610.67</v>
+        <v>1003.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5349-845-CM25</t>
+          <t>778993-67-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1164,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.544.929-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1249.71</v>
+        <v>1610.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2380-1153-CM25</t>
+          <t>5349-845-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>68073.13</v>
+        <v>1249.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1554-1162-CM25</t>
+          <t>2380-1153-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,32 +1290,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.087.242-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>927.74</v>
+        <v>68073.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5349-1558-CM25</t>
+          <t>1554-1162-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1325,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1340,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,28 +1351,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>965.87</v>
+        <v>927.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5349-1696-CM25</t>
+          <t>5349-1558-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2129.08</v>
+        <v>965.87</v>
       </c>
     </row>
     <row r="17">
@@ -1498,7 +1498,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5349-1764-CM25</t>
+          <t>5349-1696-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7726.64</v>
+        <v>2129.08</v>
       </c>
     </row>
     <row r="19">
@@ -1620,7 +1620,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5349-1940-CM25</t>
+          <t>5349-1764-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>613.11</v>
+        <v>7726.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5349-2225-CM25</t>
+          <t>5349-1940-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1481.65</v>
+        <v>613.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5349-2292-CM25</t>
+          <t>5349-2225-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1245.59</v>
+        <v>1481.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2322-926-CM25</t>
+          <t>5349-2292-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1843,32 +1843,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4881.44</v>
+        <v>1245.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5349-2606-CM25</t>
+          <t>2322-926-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1878,12 +1874,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1893,12 +1889,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1908,28 +1904,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>635.92</v>
+        <v>4881.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5349-191-CM26</t>
+          <t>5349-2606-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1363.04</v>
+        <v>635.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1554-171-CM26</t>
+          <t>5349-191-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4663.32</v>
+        <v>1363.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5349-369-CM26</t>
+          <t>1554-171-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1361.87</v>
+        <v>4663.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5349-540-CM26</t>
+          <t>5349-369-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1287.99</v>
+        <v>1361.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079486-48-CM26</t>
+          <t>5349-540-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2213,32 +2213,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11593.79</v>
+        <v>1287.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1554-748-CM26</t>
+          <t>1079486-48-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2263,12 +2259,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2278,12 +2274,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2297,13 +2293,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1305.79</v>
+        <v>11593.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5349-899-CM26</t>
+          <t>1554-748-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2313,12 +2309,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2328,12 +2324,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2343,28 +2339,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1178.73</v>
+        <v>1305.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2380-921-CM26</t>
+          <t>5349-899-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2379,22 +2379,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2404,32 +2404,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>40989.25</v>
+        <v>1178.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1554-941-CM26</t>
+          <t>2380-921-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2439,27 +2435,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2469,28 +2465,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4482.27</v>
+        <v>40989.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2322-384-CM26</t>
+          <t>1554-941-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2530,26 +2530,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>326.25</v>
+        <v>4482.27</v>
       </c>
     </row>
     <row r="35">
@@ -2620,7 +2616,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5349-1183-CM26</t>
+          <t>2322-384-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2635,7 +2631,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2645,12 +2641,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2660,28 +2656,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1582.23</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>5349-1183-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2721,32 +2721,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4700.4</v>
+        <v>1582.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>2322-382-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2761,7 +2757,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2771,12 +2767,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2786,28 +2782,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1309.09</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2322-540-CM26</t>
+          <t>5349-1254-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2817,27 +2817,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6277.96</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2380-1311-CM26</t>
+          <t>2322-540-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>35515.26</v>
+        <v>6277.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2380-1314-CM26</t>
+          <t>2380-1311-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>39063.38</v>
+        <v>35515.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2380-1334-CM26</t>
+          <t>2380-1314-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>29553.81</v>
+        <v>39063.38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1077275-25-CM26</t>
+          <t>2380-1334-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5907.57</v>
+        <v>29553.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2380-1372-CM26</t>
+          <t>1077275-25-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3127,22 +3127,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3152,32 +3152,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4904.73</v>
+        <v>5907.57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2380-1415-CM26</t>
+          <t>2380-1372-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3187,12 +3183,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3217,28 +3213,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5127.18</v>
+        <v>4904.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2380-1435-CM26</t>
+          <t>2380-1415-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4914.75</v>
+        <v>5127.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2380-1438-CM26</t>
+          <t>2380-1435-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25246.75</v>
+        <v>4914.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5349-1864-CM26</t>
+          <t>2380-1438-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3370,27 +3370,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1362.18</v>
+        <v>25246.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5349-1928-CM26</t>
+          <t>5349-1864-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3476,13 +3476,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3566.07</v>
+        <v>1362.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5349-1927-CM26</t>
+          <t>5349-1928-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3543,7 +3543,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5349-1977-CM26</t>
+          <t>5349-1927-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3598,13 +3598,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1111.39</v>
+        <v>3566.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5349-1978-CM26</t>
+          <t>5349-1977-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3659,71 +3659,132 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1234.88</v>
+        <v>1111.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>5349-1978-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1234.88</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>778993-147-CM26</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>61.946.100-2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>ADM SPA.</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="n">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
         <v>5143.83</v>
       </c>
     </row>
